--- a/mis-portal/reports/2026-06-08/ADR_20260608.xlsx
+++ b/mis-portal/reports/2026-06-08/ADR_20260608.xlsx
@@ -18,8 +18,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="DD-MMM-YYYY"/>
+    <numFmt numFmtId="166" formatCode="₹#,##0.00"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,12 +51,16 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +85,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F7FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -126,7 +144,40 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -623,109 +674,272 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>MF — Equity Funds</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ICICI Prudential Dynamic Asset Allocation Active FOF-Growth (formerly ICICI Prudential Advisor Series</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>45527</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>1650383.84</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>1781094.86</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>1781094.855</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>1788684.49</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>-7589.63</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>87263.10000000001</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>130711.02</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0.05151799999999999</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.07919999999999999</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>0.043487</v>
+      </c>
+      <c r="M8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>SBI Children's Fund - Investment Plan Regular Growth</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="13" t="n">
+        <v>984167.5699999999</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>1151772.98</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>1151772.9825</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>1148106.71</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>3666.27</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>144215.75</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>167605.41</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>0.143134</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>0.170302</v>
+      </c>
+      <c r="L9" s="14" t="n"/>
+      <c r="M9" s="15" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>SBI Children's Fund - Savings Plan Regular Growth</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="8" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>176162.58</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>176162.5822</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>174777.67</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>1384.91</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>8700.940000000001</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>26162.58</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0.051958</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.174417</v>
+      </c>
+      <c r="L10" s="9" t="n"/>
+      <c r="M10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Total MF — Equity Funds</t>
+        </is>
+      </c>
+      <c r="C11" s="16">
+        <f>SUM(C8:C10)</f>
+        <v/>
+      </c>
+      <c r="D11" s="16">
+        <f>SUM(D8:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="16">
+        <f>SUM(E8:E10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="16">
+        <f>SUM(F8:F10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="16">
+        <f>SUM(G8:G10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="16">
+        <f>SUM(H8:H10)</f>
+        <v/>
+      </c>
+      <c r="I11" s="16">
+        <f>SUM(I8:I10)</f>
+        <v/>
+      </c>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>B. TOTAL EQUITY</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>ALTERNATES</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>D. TOTAL ALTERNATES</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>E. Funds in Transit</t>
-        </is>
-      </c>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>ALTERNATES</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>D. TOTAL ALTERNATES</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>E. Funds in Transit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>F. Broker Balance</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>G. Funds in Bank</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>H. GRAND TOTAL (A+B+D+E+F+G)</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Report generated on 08 Jun 2026 10:06 UTC  |  MF data auto-populated from CAS  |  Manual inputs as last updated in portal</t>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Report generated on 08 Jun 2026 11:25 UTC  |  MF data auto-populated from CAS  |  Manual inputs as last updated in portal</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A19:M19"/>
     <mergeCell ref="A14:M14"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A17:M17"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A21:M21"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A25:M25"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
